--- a/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Spain installed capacity, month-end (Red Electrica REData) (to Nov/26)</a:t>
+              <a:t>Spain installed capacity, month-end (Red Electrica REData) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -190,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$72</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$72</f>
+              <f>'Chart'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$72</f>
+              <f>'Chart'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$72</f>
+              <f>'Chart'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$72</f>
+              <f>'Chart'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -330,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$72</f>
+              <f>'Chart'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -358,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$72</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$72</f>
+              <f>'Chart'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -464,7 +464,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Spain installed capacity net additions of solar and wind per month (to Nov/26)</a:t>
+              <a:t>Spain installed capacity net additions of solar and wind per month (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -494,12 +494,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$71</f>
+              <f>'Chart - Net additions'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$B$2:$B$71</f>
+              <f>'Chart - Net additions'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -522,12 +522,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Net additions'!$A$2:$A$71</f>
+              <f>'Chart - Net additions'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Net additions'!$C$2:$C$71</f>
+              <f>'Chart - Net additions'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2898,32 +2898,6 @@
         <v>3.1354</v>
       </c>
       <c r="H71" t="n">
-        <v>1.4993</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B72" t="n">
-        <v>58.8973</v>
-      </c>
-      <c r="C72" t="n">
-        <v>33.7049</v>
-      </c>
-      <c r="D72" t="n">
-        <v>27.3873</v>
-      </c>
-      <c r="E72" t="n">
-        <v>17.0807</v>
-      </c>
-      <c r="F72" t="n">
-        <v>7.1173</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3.1382</v>
-      </c>
-      <c r="H72" t="n">
         <v>1.4993</v>
       </c>
     </row>
@@ -2939,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3719,17 +3693,6 @@
       </c>
       <c r="C70" t="n">
         <v>-3.399999999994179</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B71" t="n">
-        <v>307.3000000000029</v>
-      </c>
-      <c r="C71" t="n">
-        <v>110.5999999999985</v>
       </c>
     </row>
   </sheetData>
@@ -3744,7 +3707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7337,56 +7300,6 @@
       </c>
       <c r="R71" t="n">
         <v>154036.8</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B72" t="n">
-        <v>17080.7</v>
-      </c>
-      <c r="C72" t="n">
-        <v>27387.3</v>
-      </c>
-      <c r="D72" t="n">
-        <v>33704.9</v>
-      </c>
-      <c r="E72" t="n">
-        <v>58897.3</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1499.3</v>
-      </c>
-      <c r="G72" t="n">
-        <v>7117.3</v>
-      </c>
-      <c r="H72" t="n">
-        <v>1821.1</v>
-      </c>
-      <c r="I72" t="n">
-        <v>1317.1</v>
-      </c>
-      <c r="J72" t="n">
-        <v>5586.4</v>
-      </c>
-      <c r="K72" t="n">
-        <v>154411.5</v>
-      </c>
-      <c r="N72" t="n">
-        <v>56595.2</v>
-      </c>
-      <c r="O72" t="n">
-        <v>2302.1</v>
-      </c>
-      <c r="P72" t="n">
-        <v>26250.1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>5175.8</v>
-      </c>
-      <c r="R72" t="n">
-        <v>154411.5</v>
       </c>
     </row>
   </sheetData>
@@ -9088,12 +9001,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>2026-10-12 04:52 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>last-update 2026-10-01T18:48:27.000+02:00</t>
+          <t>last-update 2026-10-01T18:07:42.000+02:00</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:52 UTC</t>
+          <t>2026-10-12 04:54 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/spain_power_capacity_monthly.xlsx
@@ -9001,7 +9001,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:54 UTC</t>
+          <t>2026-10-28 01:13 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
